--- a/lessons/codex-ai-video-workshop/materials/reference-results/03-excel/october-sales-report.xlsx
+++ b/lessons/codex-ai-video-workshop/materials/reference-results/03-excel/october-sales-report.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R87783724de4c4d68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clean orders" sheetId="2" r:id="Rffe305ada1954b8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="3" r:id="Ra24399f0e66546fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb87c54d556f3495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clean orders" sheetId="2" r:id="R225d69d06a4640bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="3" r:id="R35d5857b9b5e48e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -322,7 +322,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Fictional training reference; signed order values, not recognized revenue.</x:v>
+        <x:v>Order processing exercise: signed order values.</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
